--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647318</v>
+        <v>122647261</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551748</v>
+        <v>551687</v>
       </c>
       <c r="R2" t="n">
-        <v>7246419</v>
+        <v>7246322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647262</v>
+        <v>122647318</v>
       </c>
       <c r="B3" t="n">
-        <v>90829</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551686</v>
+        <v>551748</v>
       </c>
       <c r="R3" t="n">
-        <v>7246330</v>
+        <v>7246419</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647319</v>
+        <v>122647276</v>
       </c>
       <c r="B4" t="n">
-        <v>97194</v>
+        <v>90829</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551763</v>
+        <v>551728</v>
       </c>
       <c r="R4" t="n">
-        <v>7246423</v>
+        <v>7246341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647277</v>
+        <v>122647278</v>
       </c>
       <c r="B5" t="n">
         <v>74757</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551716</v>
+        <v>551729</v>
       </c>
       <c r="R5" t="n">
-        <v>7246359</v>
+        <v>7246354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647258</v>
+        <v>122647259</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
         <v>551667</v>
       </c>
       <c r="R6" t="n">
-        <v>7246282</v>
+        <v>7246288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647279</v>
+        <v>122647294</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551715</v>
+        <v>551726</v>
       </c>
       <c r="R7" t="n">
-        <v>7246376</v>
+        <v>7246369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647293</v>
+        <v>122647316</v>
       </c>
       <c r="B8" t="n">
         <v>90851</v>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551730</v>
+        <v>551762</v>
       </c>
       <c r="R8" t="n">
-        <v>7246351</v>
+        <v>7246403</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647320</v>
+        <v>122647258</v>
       </c>
       <c r="B9" t="n">
-        <v>74757</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551763</v>
+        <v>551667</v>
       </c>
       <c r="R9" t="n">
-        <v>7246410</v>
+        <v>7246282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1503,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647316</v>
+        <v>122647257</v>
       </c>
       <c r="B10" t="n">
-        <v>90851</v>
+        <v>8430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551762</v>
+        <v>551664</v>
       </c>
       <c r="R10" t="n">
-        <v>7246403</v>
+        <v>7246288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,6 +1614,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647123</v>
+        <v>122647277</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>74757</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1665,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551884</v>
+        <v>551716</v>
       </c>
       <c r="R11" t="n">
-        <v>7246571</v>
+        <v>7246359</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1744,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1740,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647122</v>
+        <v>122647314</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1780,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551874</v>
+        <v>551740</v>
       </c>
       <c r="R12" t="n">
-        <v>7246567</v>
+        <v>7246367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1850,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647294</v>
+        <v>122647293</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551726</v>
+        <v>551730</v>
       </c>
       <c r="R13" t="n">
-        <v>7246369</v>
+        <v>7246351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,11 +1937,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647292</v>
+        <v>122647315</v>
       </c>
       <c r="B14" t="n">
-        <v>90851</v>
+        <v>90829</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551712</v>
+        <v>551738</v>
       </c>
       <c r="R14" t="n">
-        <v>7246357</v>
+        <v>7246373</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647314</v>
+        <v>122647292</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2089,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551740</v>
+        <v>551712</v>
       </c>
       <c r="R15" t="n">
-        <v>7246367</v>
+        <v>7246357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647261</v>
+        <v>122647122</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2209,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551687</v>
+        <v>551874</v>
       </c>
       <c r="R16" t="n">
-        <v>7246322</v>
+        <v>7246567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,7 +2274,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2275,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647260</v>
+        <v>122647123</v>
       </c>
       <c r="B17" t="n">
-        <v>91771</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,25 +2297,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551667</v>
+        <v>551884</v>
       </c>
       <c r="R17" t="n">
-        <v>7246311</v>
+        <v>7246571</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2380,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2381,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647257</v>
+        <v>122647295</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551664</v>
+        <v>551732</v>
       </c>
       <c r="R18" t="n">
-        <v>7246288</v>
+        <v>7246362</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2461,7 +2471,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647295</v>
+        <v>122647320</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>74757</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551732</v>
+        <v>551763</v>
       </c>
       <c r="R19" t="n">
-        <v>7246362</v>
+        <v>7246410</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,11 +2578,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647259</v>
+        <v>122647319</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>97194</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,21 +2624,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551667</v>
+        <v>551763</v>
       </c>
       <c r="R20" t="n">
-        <v>7246288</v>
+        <v>7246423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2679,11 +2684,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647315</v>
+        <v>122647279</v>
       </c>
       <c r="B21" t="n">
-        <v>90829</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551738</v>
+        <v>551715</v>
       </c>
       <c r="R21" t="n">
-        <v>7246373</v>
+        <v>7246376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647276</v>
+        <v>122647260</v>
       </c>
       <c r="B22" t="n">
-        <v>90829</v>
+        <v>91771</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2832,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551728</v>
+        <v>551667</v>
       </c>
       <c r="R22" t="n">
-        <v>7246341</v>
+        <v>7246311</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647278</v>
+        <v>122647262</v>
       </c>
       <c r="B23" t="n">
-        <v>74757</v>
+        <v>90829</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551729</v>
+        <v>551686</v>
       </c>
       <c r="R23" t="n">
-        <v>7246354</v>
+        <v>7246330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647261</v>
+        <v>122647294</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551687</v>
+        <v>551726</v>
       </c>
       <c r="R2" t="n">
-        <v>7246322</v>
+        <v>7246369</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647318</v>
+        <v>122647277</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>74758</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551748</v>
+        <v>551716</v>
       </c>
       <c r="R3" t="n">
-        <v>7246419</v>
+        <v>7246359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647276</v>
+        <v>122647318</v>
       </c>
       <c r="B4" t="n">
-        <v>90829</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551728</v>
+        <v>551748</v>
       </c>
       <c r="R4" t="n">
-        <v>7246341</v>
+        <v>7246419</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647278</v>
+        <v>122647292</v>
       </c>
       <c r="B5" t="n">
-        <v>74757</v>
+        <v>90852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551729</v>
+        <v>551712</v>
       </c>
       <c r="R5" t="n">
-        <v>7246354</v>
+        <v>7246357</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647259</v>
+        <v>122647315</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>90830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551667</v>
+        <v>551738</v>
       </c>
       <c r="R6" t="n">
-        <v>7246288</v>
+        <v>7246373</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,11 +1180,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647294</v>
+        <v>122647261</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551726</v>
+        <v>551687</v>
       </c>
       <c r="R7" t="n">
-        <v>7246369</v>
+        <v>7246322</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647316</v>
+        <v>122647259</v>
       </c>
       <c r="B8" t="n">
-        <v>90851</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551762</v>
+        <v>551667</v>
       </c>
       <c r="R8" t="n">
-        <v>7246403</v>
+        <v>7246288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1392,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647258</v>
+        <v>122647319</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>97195</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551667</v>
+        <v>551763</v>
       </c>
       <c r="R9" t="n">
-        <v>7246282</v>
+        <v>7246423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647257</v>
+        <v>122647260</v>
       </c>
       <c r="B10" t="n">
-        <v>8430</v>
+        <v>91772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551664</v>
+        <v>551667</v>
       </c>
       <c r="R10" t="n">
-        <v>7246288</v>
+        <v>7246311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,11 +1609,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647277</v>
+        <v>122647295</v>
       </c>
       <c r="B11" t="n">
-        <v>74757</v>
+        <v>57495</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551716</v>
+        <v>551732</v>
       </c>
       <c r="R11" t="n">
-        <v>7246359</v>
+        <v>7246362</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647314</v>
+        <v>122647122</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551740</v>
+        <v>551874</v>
       </c>
       <c r="R12" t="n">
-        <v>7246367</v>
+        <v>7246567</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1845,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1861,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647293</v>
+        <v>122647278</v>
       </c>
       <c r="B13" t="n">
-        <v>90851</v>
+        <v>74758</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551730</v>
+        <v>551729</v>
       </c>
       <c r="R13" t="n">
-        <v>7246351</v>
+        <v>7246354</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647315</v>
+        <v>122647262</v>
       </c>
       <c r="B14" t="n">
-        <v>90829</v>
+        <v>90830</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551738</v>
+        <v>551686</v>
       </c>
       <c r="R14" t="n">
-        <v>7246373</v>
+        <v>7246330</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647292</v>
+        <v>122647293</v>
       </c>
       <c r="B15" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551712</v>
+        <v>551730</v>
       </c>
       <c r="R15" t="n">
-        <v>7246357</v>
+        <v>7246351</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647122</v>
+        <v>122647320</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>74758</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2190,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551874</v>
+        <v>551763</v>
       </c>
       <c r="R16" t="n">
-        <v>7246567</v>
+        <v>7246410</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2269,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2285,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647123</v>
+        <v>122647276</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>90830</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551884</v>
+        <v>551728</v>
       </c>
       <c r="R17" t="n">
-        <v>7246571</v>
+        <v>7246341</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2375,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2391,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647295</v>
+        <v>122647123</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,20 +2398,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2431,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551732</v>
+        <v>551884</v>
       </c>
       <c r="R18" t="n">
-        <v>7246362</v>
+        <v>7246571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,11 +2464,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2491,7 +2481,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2502,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647320</v>
+        <v>122647257</v>
       </c>
       <c r="B19" t="n">
-        <v>74757</v>
+        <v>8430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2504,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551763</v>
+        <v>551664</v>
       </c>
       <c r="R19" t="n">
-        <v>7246410</v>
+        <v>7246288</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,6 +2568,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647319</v>
+        <v>122647314</v>
       </c>
       <c r="B20" t="n">
-        <v>97194</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551763</v>
+        <v>551740</v>
       </c>
       <c r="R20" t="n">
-        <v>7246423</v>
+        <v>7246367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647279</v>
+        <v>122647316</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2725,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551715</v>
+        <v>551762</v>
       </c>
       <c r="R21" t="n">
-        <v>7246376</v>
+        <v>7246403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647260</v>
+        <v>122647279</v>
       </c>
       <c r="B22" t="n">
-        <v>91771</v>
+        <v>78657</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2827,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551667</v>
+        <v>551715</v>
       </c>
       <c r="R22" t="n">
-        <v>7246311</v>
+        <v>7246376</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647262</v>
+        <v>122647258</v>
       </c>
       <c r="B23" t="n">
-        <v>90829</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2937,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551686</v>
+        <v>551667</v>
       </c>
       <c r="R23" t="n">
-        <v>7246330</v>
+        <v>7246282</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,6 +2997,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647315</v>
+        <v>122647259</v>
       </c>
       <c r="B6" t="n">
-        <v>90830</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551738</v>
+        <v>551667</v>
       </c>
       <c r="R6" t="n">
-        <v>7246373</v>
+        <v>7246288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647261</v>
+        <v>122647315</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>90830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551687</v>
+        <v>551738</v>
       </c>
       <c r="R7" t="n">
-        <v>7246322</v>
+        <v>7246373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647259</v>
+        <v>122647261</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551667</v>
+        <v>551687</v>
       </c>
       <c r="R8" t="n">
-        <v>7246288</v>
+        <v>7246322</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,11 +1397,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647319</v>
+        <v>122647260</v>
       </c>
       <c r="B9" t="n">
-        <v>97195</v>
+        <v>91772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551763</v>
+        <v>551667</v>
       </c>
       <c r="R9" t="n">
-        <v>7246423</v>
+        <v>7246311</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647260</v>
+        <v>122647295</v>
       </c>
       <c r="B10" t="n">
-        <v>91772</v>
+        <v>57495</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551667</v>
+        <v>551732</v>
       </c>
       <c r="R10" t="n">
-        <v>7246311</v>
+        <v>7246362</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,6 +1609,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647295</v>
+        <v>122647319</v>
       </c>
       <c r="B11" t="n">
-        <v>57495</v>
+        <v>97195</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551732</v>
+        <v>551763</v>
       </c>
       <c r="R11" t="n">
-        <v>7246362</v>
+        <v>7246423</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,11 +1720,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647279</v>
+        <v>122647258</v>
       </c>
       <c r="B22" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551715</v>
+        <v>551667</v>
       </c>
       <c r="R22" t="n">
-        <v>7246376</v>
+        <v>7246282</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,6 +2891,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2921,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647258</v>
+        <v>122647279</v>
       </c>
       <c r="B23" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551667</v>
+        <v>551715</v>
       </c>
       <c r="R23" t="n">
-        <v>7246282</v>
+        <v>7246376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,11 +3002,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647294</v>
+        <v>122647316</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551726</v>
+        <v>551762</v>
       </c>
       <c r="R2" t="n">
-        <v>7246369</v>
+        <v>7246403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647277</v>
+        <v>122647261</v>
       </c>
       <c r="B3" t="n">
-        <v>74758</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551716</v>
+        <v>551687</v>
       </c>
       <c r="R3" t="n">
-        <v>7246359</v>
+        <v>7246322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647318</v>
+        <v>122647277</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>74761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551748</v>
+        <v>551716</v>
       </c>
       <c r="R4" t="n">
-        <v>7246419</v>
+        <v>7246359</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647292</v>
+        <v>122647315</v>
       </c>
       <c r="B5" t="n">
-        <v>90852</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551712</v>
+        <v>551738</v>
       </c>
       <c r="R5" t="n">
-        <v>7246357</v>
+        <v>7246373</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647259</v>
+        <v>122647276</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>90833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551667</v>
+        <v>551728</v>
       </c>
       <c r="R6" t="n">
-        <v>7246288</v>
+        <v>7246341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647315</v>
+        <v>122647318</v>
       </c>
       <c r="B7" t="n">
-        <v>90830</v>
+        <v>57537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551738</v>
+        <v>551748</v>
       </c>
       <c r="R7" t="n">
-        <v>7246373</v>
+        <v>7246419</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647261</v>
+        <v>122647259</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551687</v>
+        <v>551667</v>
       </c>
       <c r="R8" t="n">
-        <v>7246322</v>
+        <v>7246288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,7 +1425,7 @@
         <v>122647260</v>
       </c>
       <c r="B9" t="n">
-        <v>91772</v>
+        <v>91775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647295</v>
+        <v>122647278</v>
       </c>
       <c r="B10" t="n">
-        <v>57495</v>
+        <v>74761</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551732</v>
+        <v>551729</v>
       </c>
       <c r="R10" t="n">
-        <v>7246362</v>
+        <v>7246354</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,11 +1604,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647319</v>
+        <v>122647122</v>
       </c>
       <c r="B11" t="n">
-        <v>97195</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551763</v>
+        <v>551874</v>
       </c>
       <c r="R11" t="n">
-        <v>7246423</v>
+        <v>7246567</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1729,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1750,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647122</v>
+        <v>122647258</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551874</v>
+        <v>551667</v>
       </c>
       <c r="R12" t="n">
-        <v>7246567</v>
+        <v>7246282</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,6 +1818,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1845,7 +1840,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1856,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647278</v>
+        <v>122647293</v>
       </c>
       <c r="B13" t="n">
-        <v>74758</v>
+        <v>90855</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551729</v>
+        <v>551730</v>
       </c>
       <c r="R13" t="n">
-        <v>7246354</v>
+        <v>7246351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647262</v>
+        <v>122647292</v>
       </c>
       <c r="B14" t="n">
-        <v>90830</v>
+        <v>90855</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551686</v>
+        <v>551712</v>
       </c>
       <c r="R14" t="n">
-        <v>7246330</v>
+        <v>7246357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647293</v>
+        <v>122647319</v>
       </c>
       <c r="B15" t="n">
-        <v>90852</v>
+        <v>97198</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551730</v>
+        <v>551763</v>
       </c>
       <c r="R15" t="n">
-        <v>7246351</v>
+        <v>7246423</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647320</v>
+        <v>122647257</v>
       </c>
       <c r="B16" t="n">
-        <v>74758</v>
+        <v>8430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551763</v>
+        <v>551664</v>
       </c>
       <c r="R16" t="n">
-        <v>7246410</v>
+        <v>7246288</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,6 +2245,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647276</v>
+        <v>122647320</v>
       </c>
       <c r="B17" t="n">
-        <v>90830</v>
+        <v>74761</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551728</v>
+        <v>551763</v>
       </c>
       <c r="R17" t="n">
-        <v>7246341</v>
+        <v>7246410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647257</v>
+        <v>122647295</v>
       </c>
       <c r="B19" t="n">
-        <v>8430</v>
+        <v>57495</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551664</v>
+        <v>551732</v>
       </c>
       <c r="R19" t="n">
-        <v>7246288</v>
+        <v>7246362</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2606,7 @@
         <v>122647314</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647316</v>
+        <v>122647294</v>
       </c>
       <c r="B21" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,21 +2725,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551762</v>
+        <v>551726</v>
       </c>
       <c r="R21" t="n">
-        <v>7246403</v>
+        <v>7246369</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,6 +2785,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647258</v>
+        <v>122647279</v>
       </c>
       <c r="B22" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551667</v>
+        <v>551715</v>
       </c>
       <c r="R22" t="n">
-        <v>7246282</v>
+        <v>7246376</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,11 +2896,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647279</v>
+        <v>122647262</v>
       </c>
       <c r="B23" t="n">
-        <v>78657</v>
+        <v>90833</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551715</v>
+        <v>551686</v>
       </c>
       <c r="R23" t="n">
-        <v>7246376</v>
+        <v>7246330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647316</v>
+        <v>122647278</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
+        <v>74761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551762</v>
+        <v>551729</v>
       </c>
       <c r="R2" t="n">
-        <v>7246403</v>
+        <v>7246354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647261</v>
+        <v>122647320</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551687</v>
+        <v>551763</v>
       </c>
       <c r="R3" t="n">
-        <v>7246322</v>
+        <v>7246410</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647277</v>
+        <v>122647292</v>
       </c>
       <c r="B4" t="n">
-        <v>74761</v>
+        <v>90855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551716</v>
+        <v>551712</v>
       </c>
       <c r="R4" t="n">
-        <v>7246359</v>
+        <v>7246357</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647276</v>
+        <v>122647294</v>
       </c>
       <c r="B6" t="n">
-        <v>90833</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551728</v>
+        <v>551726</v>
       </c>
       <c r="R6" t="n">
-        <v>7246341</v>
+        <v>7246369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647318</v>
+        <v>122647276</v>
       </c>
       <c r="B7" t="n">
-        <v>57537</v>
+        <v>90833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551748</v>
+        <v>551728</v>
       </c>
       <c r="R7" t="n">
-        <v>7246419</v>
+        <v>7246341</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647259</v>
+        <v>122647262</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>90833</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551667</v>
+        <v>551686</v>
       </c>
       <c r="R8" t="n">
-        <v>7246288</v>
+        <v>7246330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647260</v>
+        <v>122647258</v>
       </c>
       <c r="B9" t="n">
-        <v>91775</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
         <v>551667</v>
       </c>
       <c r="R9" t="n">
-        <v>7246311</v>
+        <v>7246282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1498,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647278</v>
+        <v>122647316</v>
       </c>
       <c r="B10" t="n">
-        <v>74761</v>
+        <v>90855</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551729</v>
+        <v>551762</v>
       </c>
       <c r="R10" t="n">
-        <v>7246354</v>
+        <v>7246403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647258</v>
+        <v>122647279</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551667</v>
+        <v>551715</v>
       </c>
       <c r="R12" t="n">
-        <v>7246282</v>
+        <v>7246376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647293</v>
+        <v>122647319</v>
       </c>
       <c r="B13" t="n">
-        <v>90855</v>
+        <v>97198</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551730</v>
+        <v>551763</v>
       </c>
       <c r="R13" t="n">
-        <v>7246351</v>
+        <v>7246423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647292</v>
+        <v>122647318</v>
       </c>
       <c r="B14" t="n">
-        <v>90855</v>
+        <v>57537</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551712</v>
+        <v>551748</v>
       </c>
       <c r="R14" t="n">
-        <v>7246357</v>
+        <v>7246419</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647319</v>
+        <v>122647259</v>
       </c>
       <c r="B15" t="n">
-        <v>97198</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2079,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551763</v>
+        <v>551667</v>
       </c>
       <c r="R15" t="n">
-        <v>7246423</v>
+        <v>7246288</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,6 +2139,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647257</v>
+        <v>122647123</v>
       </c>
       <c r="B16" t="n">
-        <v>8430</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2186,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551664</v>
+        <v>551884</v>
       </c>
       <c r="R16" t="n">
-        <v>7246288</v>
+        <v>7246571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,11 +2252,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gnag</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647320</v>
+        <v>122647277</v>
       </c>
       <c r="B17" t="n">
         <v>74761</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551763</v>
+        <v>551716</v>
       </c>
       <c r="R17" t="n">
-        <v>7246410</v>
+        <v>7246359</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647123</v>
+        <v>122647257</v>
       </c>
       <c r="B18" t="n">
-        <v>57384</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,25 +2398,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551884</v>
+        <v>551664</v>
       </c>
       <c r="R18" t="n">
-        <v>7246571</v>
+        <v>7246288</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,6 +2464,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gnag</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2481,7 +2486,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2492,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647295</v>
+        <v>122647314</v>
       </c>
       <c r="B19" t="n">
-        <v>57495</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551732</v>
+        <v>551740</v>
       </c>
       <c r="R19" t="n">
-        <v>7246362</v>
+        <v>7246367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,11 +2573,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,7 +2603,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647314</v>
+        <v>122647261</v>
       </c>
       <c r="B20" t="n">
         <v>78660</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551740</v>
+        <v>551687</v>
       </c>
       <c r="R20" t="n">
-        <v>7246367</v>
+        <v>7246322</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647294</v>
+        <v>122647295</v>
       </c>
       <c r="B21" t="n">
-        <v>57384</v>
+        <v>57495</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,20 +2721,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551726</v>
+        <v>551732</v>
       </c>
       <c r="R21" t="n">
-        <v>7246369</v>
+        <v>7246362</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647279</v>
+        <v>122647260</v>
       </c>
       <c r="B22" t="n">
-        <v>78660</v>
+        <v>91775</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2832,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551715</v>
+        <v>551667</v>
       </c>
       <c r="R22" t="n">
-        <v>7246376</v>
+        <v>7246311</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647262</v>
+        <v>122647293</v>
       </c>
       <c r="B23" t="n">
-        <v>90833</v>
+        <v>90855</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551686</v>
+        <v>551730</v>
       </c>
       <c r="R23" t="n">
-        <v>7246330</v>
+        <v>7246351</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647122</v>
+        <v>122647319</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>97198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551874</v>
+        <v>551763</v>
       </c>
       <c r="R11" t="n">
-        <v>7246567</v>
+        <v>7246423</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647279</v>
+        <v>122647122</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551715</v>
+        <v>551874</v>
       </c>
       <c r="R12" t="n">
-        <v>7246376</v>
+        <v>7246567</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647319</v>
+        <v>122647279</v>
       </c>
       <c r="B13" t="n">
-        <v>97198</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551763</v>
+        <v>551715</v>
       </c>
       <c r="R13" t="n">
-        <v>7246423</v>
+        <v>7246376</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647319</v>
+        <v>122647122</v>
       </c>
       <c r="B11" t="n">
-        <v>97198</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551763</v>
+        <v>551874</v>
       </c>
       <c r="R11" t="n">
-        <v>7246423</v>
+        <v>7246567</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647122</v>
+        <v>122647279</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551874</v>
+        <v>551715</v>
       </c>
       <c r="R12" t="n">
-        <v>7246567</v>
+        <v>7246376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647279</v>
+        <v>122647319</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>97198</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551715</v>
+        <v>551763</v>
       </c>
       <c r="R13" t="n">
-        <v>7246376</v>
+        <v>7246423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647278</v>
+        <v>122647292</v>
       </c>
       <c r="B2" t="n">
-        <v>74761</v>
+        <v>90958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551729</v>
+        <v>551712</v>
       </c>
       <c r="R2" t="n">
-        <v>7246354</v>
+        <v>7246357</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647320</v>
+        <v>122647319</v>
       </c>
       <c r="B3" t="n">
-        <v>74761</v>
+        <v>97301</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,7 +824,7 @@
         <v>551763</v>
       </c>
       <c r="R3" t="n">
-        <v>7246410</v>
+        <v>7246423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647292</v>
+        <v>122647262</v>
       </c>
       <c r="B4" t="n">
-        <v>90855</v>
+        <v>90936</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551712</v>
+        <v>551686</v>
       </c>
       <c r="R4" t="n">
-        <v>7246357</v>
+        <v>7246330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647315</v>
+        <v>122647316</v>
       </c>
       <c r="B5" t="n">
-        <v>90833</v>
+        <v>90958</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551738</v>
+        <v>551762</v>
       </c>
       <c r="R5" t="n">
-        <v>7246373</v>
+        <v>7246403</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647294</v>
+        <v>122647258</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551726</v>
+        <v>551667</v>
       </c>
       <c r="R6" t="n">
-        <v>7246369</v>
+        <v>7246282</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647276</v>
+        <v>122647259</v>
       </c>
       <c r="B7" t="n">
-        <v>90833</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551728</v>
+        <v>551667</v>
       </c>
       <c r="R7" t="n">
-        <v>7246341</v>
+        <v>7246288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647262</v>
+        <v>122647276</v>
       </c>
       <c r="B8" t="n">
-        <v>90833</v>
+        <v>90936</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551686</v>
+        <v>551728</v>
       </c>
       <c r="R8" t="n">
-        <v>7246330</v>
+        <v>7246341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647258</v>
+        <v>122647294</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551667</v>
+        <v>551726</v>
       </c>
       <c r="R9" t="n">
-        <v>7246282</v>
+        <v>7246369</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1507,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647316</v>
+        <v>122647295</v>
       </c>
       <c r="B10" t="n">
-        <v>90855</v>
+        <v>57589</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551762</v>
+        <v>551732</v>
       </c>
       <c r="R10" t="n">
-        <v>7246403</v>
+        <v>7246362</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,6 +1614,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647122</v>
+        <v>122647314</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551874</v>
+        <v>551740</v>
       </c>
       <c r="R11" t="n">
-        <v>7246567</v>
+        <v>7246367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1744,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1745,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647279</v>
+        <v>122647315</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>90936</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551715</v>
+        <v>551738</v>
       </c>
       <c r="R12" t="n">
-        <v>7246376</v>
+        <v>7246373</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647319</v>
+        <v>122647257</v>
       </c>
       <c r="B13" t="n">
-        <v>97198</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551763</v>
+        <v>551664</v>
       </c>
       <c r="R13" t="n">
-        <v>7246423</v>
+        <v>7246288</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,6 +1937,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647318</v>
+        <v>122647277</v>
       </c>
       <c r="B14" t="n">
-        <v>57537</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551748</v>
+        <v>551716</v>
       </c>
       <c r="R14" t="n">
-        <v>7246419</v>
+        <v>7246359</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647259</v>
+        <v>122647260</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>91878</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2094,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,7 +2121,7 @@
         <v>551667</v>
       </c>
       <c r="R15" t="n">
-        <v>7246288</v>
+        <v>7246311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,11 +2154,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2177,7 +2187,7 @@
         <v>122647123</v>
       </c>
       <c r="B16" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647277</v>
+        <v>122647278</v>
       </c>
       <c r="B17" t="n">
-        <v>74761</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551716</v>
+        <v>551729</v>
       </c>
       <c r="R17" t="n">
-        <v>7246359</v>
+        <v>7246354</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647257</v>
+        <v>122647318</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,25 +2408,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551664</v>
+        <v>551748</v>
       </c>
       <c r="R18" t="n">
-        <v>7246288</v>
+        <v>7246419</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,11 +2472,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647314</v>
+        <v>122647320</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
+        <v>74863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551740</v>
+        <v>551763</v>
       </c>
       <c r="R19" t="n">
-        <v>7246367</v>
+        <v>7246410</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647261</v>
+        <v>122647293</v>
       </c>
       <c r="B20" t="n">
-        <v>78660</v>
+        <v>90958</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,21 +2624,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551687</v>
+        <v>551730</v>
       </c>
       <c r="R20" t="n">
-        <v>7246322</v>
+        <v>7246351</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647295</v>
+        <v>122647261</v>
       </c>
       <c r="B21" t="n">
-        <v>57495</v>
+        <v>78762</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,25 +2726,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551732</v>
+        <v>551687</v>
       </c>
       <c r="R21" t="n">
-        <v>7246362</v>
+        <v>7246322</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,11 +2790,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647260</v>
+        <v>122647122</v>
       </c>
       <c r="B22" t="n">
-        <v>91775</v>
+        <v>78762</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2832,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551667</v>
+        <v>551874</v>
       </c>
       <c r="R22" t="n">
-        <v>7246311</v>
+        <v>7246567</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647293</v>
+        <v>122647279</v>
       </c>
       <c r="B23" t="n">
-        <v>90855</v>
+        <v>78762</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551730</v>
+        <v>551715</v>
       </c>
       <c r="R23" t="n">
-        <v>7246351</v>
+        <v>7246376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647276</v>
+        <v>122647295</v>
       </c>
       <c r="B8" t="n">
-        <v>90936</v>
+        <v>57589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551728</v>
+        <v>551732</v>
       </c>
       <c r="R8" t="n">
-        <v>7246341</v>
+        <v>7246362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1397,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647294</v>
+        <v>122647276</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90936</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551726</v>
+        <v>551728</v>
       </c>
       <c r="R9" t="n">
-        <v>7246369</v>
+        <v>7246341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,11 +1508,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647295</v>
+        <v>122647294</v>
       </c>
       <c r="B10" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551732</v>
+        <v>551726</v>
       </c>
       <c r="R10" t="n">
-        <v>7246362</v>
+        <v>7246369</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3 st födosökande</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647314</v>
+        <v>122647257</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>8430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,25 +1661,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551740</v>
+        <v>551664</v>
       </c>
       <c r="R11" t="n">
-        <v>7246367</v>
+        <v>7246288</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,6 +1725,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647257</v>
+        <v>122647314</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>78762</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1878,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551664</v>
+        <v>551740</v>
       </c>
       <c r="R13" t="n">
-        <v>7246288</v>
+        <v>7246367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,11 +1942,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122647292</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647319</v>
+        <v>122647320</v>
       </c>
       <c r="B3" t="n">
-        <v>97301</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,7 +824,7 @@
         <v>551763</v>
       </c>
       <c r="R3" t="n">
-        <v>7246423</v>
+        <v>7246410</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647262</v>
+        <v>122647316</v>
       </c>
       <c r="B4" t="n">
-        <v>90936</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551686</v>
+        <v>551762</v>
       </c>
       <c r="R4" t="n">
-        <v>7246330</v>
+        <v>7246403</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647316</v>
+        <v>122647257</v>
       </c>
       <c r="B5" t="n">
-        <v>90958</v>
+        <v>8430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551762</v>
+        <v>551664</v>
       </c>
       <c r="R5" t="n">
-        <v>7246403</v>
+        <v>7246288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647258</v>
+        <v>122647259</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,7 +1147,7 @@
         <v>551667</v>
       </c>
       <c r="R6" t="n">
-        <v>7246282</v>
+        <v>7246288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1184,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647259</v>
+        <v>122647262</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>90940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551667</v>
+        <v>551686</v>
       </c>
       <c r="R7" t="n">
-        <v>7246288</v>
+        <v>7246330</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647295</v>
+        <v>122647276</v>
       </c>
       <c r="B8" t="n">
-        <v>57589</v>
+        <v>90940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551732</v>
+        <v>551728</v>
       </c>
       <c r="R8" t="n">
-        <v>7246362</v>
+        <v>7246341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,11 +1397,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647276</v>
+        <v>122647278</v>
       </c>
       <c r="B9" t="n">
-        <v>90936</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551728</v>
+        <v>551729</v>
       </c>
       <c r="R9" t="n">
-        <v>7246341</v>
+        <v>7246354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647294</v>
+        <v>122647318</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551726</v>
+        <v>551748</v>
       </c>
       <c r="R10" t="n">
-        <v>7246369</v>
+        <v>7246419</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,11 +1609,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647257</v>
+        <v>122647295</v>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
+        <v>57589</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551664</v>
+        <v>551732</v>
       </c>
       <c r="R11" t="n">
-        <v>7246288</v>
+        <v>7246362</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1719,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647315</v>
+        <v>122647261</v>
       </c>
       <c r="B12" t="n">
-        <v>90936</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551738</v>
+        <v>551687</v>
       </c>
       <c r="R12" t="n">
-        <v>7246373</v>
+        <v>7246322</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647314</v>
+        <v>122647258</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551740</v>
+        <v>551667</v>
       </c>
       <c r="R13" t="n">
-        <v>7246367</v>
+        <v>7246282</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,6 +1932,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647260</v>
+        <v>122647279</v>
       </c>
       <c r="B15" t="n">
-        <v>91878</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2118,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551667</v>
+        <v>551715</v>
       </c>
       <c r="R15" t="n">
-        <v>7246311</v>
+        <v>7246376</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647123</v>
+        <v>122647122</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2224,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551884</v>
+        <v>551874</v>
       </c>
       <c r="R16" t="n">
-        <v>7246571</v>
+        <v>7246567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647278</v>
+        <v>122647294</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551729</v>
+        <v>551726</v>
       </c>
       <c r="R17" t="n">
-        <v>7246354</v>
+        <v>7246369</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,6 +2361,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647318</v>
+        <v>122647293</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551748</v>
+        <v>551730</v>
       </c>
       <c r="R18" t="n">
-        <v>7246419</v>
+        <v>7246351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647320</v>
+        <v>122647260</v>
       </c>
       <c r="B19" t="n">
-        <v>74863</v>
+        <v>91882</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551763</v>
+        <v>551667</v>
       </c>
       <c r="R19" t="n">
-        <v>7246410</v>
+        <v>7246311</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647293</v>
+        <v>122647314</v>
       </c>
       <c r="B20" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2624,21 +2624,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551730</v>
+        <v>551740</v>
       </c>
       <c r="R20" t="n">
-        <v>7246351</v>
+        <v>7246367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647261</v>
+        <v>122647123</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551687</v>
+        <v>551884</v>
       </c>
       <c r="R21" t="n">
-        <v>7246322</v>
+        <v>7246571</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647122</v>
+        <v>122647319</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>97309</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2832,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551874</v>
+        <v>551763</v>
       </c>
       <c r="R22" t="n">
-        <v>7246567</v>
+        <v>7246423</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647279</v>
+        <v>122647315</v>
       </c>
       <c r="B23" t="n">
-        <v>78762</v>
+        <v>90940</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551715</v>
+        <v>551738</v>
       </c>
       <c r="R23" t="n">
-        <v>7246376</v>
+        <v>7246373</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647292</v>
+        <v>122647259</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551712</v>
+        <v>551667</v>
       </c>
       <c r="R2" t="n">
-        <v>7246357</v>
+        <v>7246288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647320</v>
+        <v>122647293</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551763</v>
+        <v>551730</v>
       </c>
       <c r="R3" t="n">
-        <v>7246410</v>
+        <v>7246351</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647316</v>
+        <v>122647261</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551762</v>
+        <v>551687</v>
       </c>
       <c r="R4" t="n">
-        <v>7246403</v>
+        <v>7246322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647257</v>
+        <v>122647262</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
+        <v>90940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551664</v>
+        <v>551686</v>
       </c>
       <c r="R5" t="n">
-        <v>7246288</v>
+        <v>7246330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647259</v>
+        <v>122647295</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>57589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551667</v>
+        <v>551732</v>
       </c>
       <c r="R6" t="n">
-        <v>7246288</v>
+        <v>7246362</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647262</v>
+        <v>122647257</v>
       </c>
       <c r="B7" t="n">
-        <v>90940</v>
+        <v>8430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551686</v>
+        <v>551664</v>
       </c>
       <c r="R7" t="n">
-        <v>7246330</v>
+        <v>7246288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1291,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647276</v>
+        <v>122647258</v>
       </c>
       <c r="B8" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551728</v>
+        <v>551667</v>
       </c>
       <c r="R8" t="n">
-        <v>7246341</v>
+        <v>7246282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1402,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647278</v>
+        <v>122647319</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>97309</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551729</v>
+        <v>551763</v>
       </c>
       <c r="R9" t="n">
-        <v>7246354</v>
+        <v>7246423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647318</v>
+        <v>122647260</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>91882</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551748</v>
+        <v>551667</v>
       </c>
       <c r="R10" t="n">
-        <v>7246419</v>
+        <v>7246311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647295</v>
+        <v>122647279</v>
       </c>
       <c r="B11" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1661,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551732</v>
+        <v>551715</v>
       </c>
       <c r="R11" t="n">
-        <v>7246362</v>
+        <v>7246376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,11 +1725,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647261</v>
+        <v>122647278</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551687</v>
+        <v>551729</v>
       </c>
       <c r="R12" t="n">
-        <v>7246322</v>
+        <v>7246354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647258</v>
+        <v>122647314</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551667</v>
+        <v>551740</v>
       </c>
       <c r="R13" t="n">
-        <v>7246282</v>
+        <v>7246367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,11 +1937,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,7 +1967,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647277</v>
+        <v>122647320</v>
       </c>
       <c r="B14" t="n">
         <v>74863</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551716</v>
+        <v>551763</v>
       </c>
       <c r="R14" t="n">
-        <v>7246359</v>
+        <v>7246410</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647279</v>
+        <v>122647122</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551715</v>
+        <v>551874</v>
       </c>
       <c r="R15" t="n">
-        <v>7246376</v>
+        <v>7246567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647122</v>
+        <v>122647315</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551874</v>
+        <v>551738</v>
       </c>
       <c r="R16" t="n">
-        <v>7246567</v>
+        <v>7246373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647294</v>
+        <v>122647277</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551726</v>
+        <v>551716</v>
       </c>
       <c r="R17" t="n">
-        <v>7246369</v>
+        <v>7246359</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,11 +2361,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647293</v>
+        <v>122647294</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551730</v>
+        <v>551726</v>
       </c>
       <c r="R18" t="n">
-        <v>7246351</v>
+        <v>7246369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,6 +2467,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647260</v>
+        <v>122647292</v>
       </c>
       <c r="B19" t="n">
-        <v>91882</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551667</v>
+        <v>551712</v>
       </c>
       <c r="R19" t="n">
-        <v>7246311</v>
+        <v>7246357</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647314</v>
+        <v>122647316</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2624,21 +2624,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551740</v>
+        <v>551762</v>
       </c>
       <c r="R20" t="n">
-        <v>7246367</v>
+        <v>7246403</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647123</v>
+        <v>122647276</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551884</v>
+        <v>551728</v>
       </c>
       <c r="R21" t="n">
-        <v>7246571</v>
+        <v>7246341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647319</v>
+        <v>122647123</v>
       </c>
       <c r="B22" t="n">
-        <v>97309</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2832,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551763</v>
+        <v>551884</v>
       </c>
       <c r="R22" t="n">
-        <v>7246423</v>
+        <v>7246571</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647315</v>
+        <v>122647318</v>
       </c>
       <c r="B23" t="n">
-        <v>90940</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551738</v>
+        <v>551748</v>
       </c>
       <c r="R23" t="n">
-        <v>7246373</v>
+        <v>7246419</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647259</v>
+        <v>122647315</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>90940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551667</v>
+        <v>551738</v>
       </c>
       <c r="R2" t="n">
-        <v>7246288</v>
+        <v>7246373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647293</v>
+        <v>122647276</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>90940</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551730</v>
+        <v>551728</v>
       </c>
       <c r="R3" t="n">
-        <v>7246351</v>
+        <v>7246341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647261</v>
+        <v>122647295</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551687</v>
+        <v>551732</v>
       </c>
       <c r="R4" t="n">
-        <v>7246322</v>
+        <v>7246362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647262</v>
+        <v>122647319</v>
       </c>
       <c r="B5" t="n">
-        <v>90940</v>
+        <v>97311</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551686</v>
+        <v>551763</v>
       </c>
       <c r="R5" t="n">
-        <v>7246330</v>
+        <v>7246423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647295</v>
+        <v>122647314</v>
       </c>
       <c r="B6" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551732</v>
+        <v>551740</v>
       </c>
       <c r="R6" t="n">
-        <v>7246362</v>
+        <v>7246367</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,11 +1180,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647257</v>
+        <v>122647293</v>
       </c>
       <c r="B7" t="n">
-        <v>8430</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551664</v>
+        <v>551730</v>
       </c>
       <c r="R7" t="n">
-        <v>7246288</v>
+        <v>7246351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647258</v>
+        <v>122647292</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551667</v>
+        <v>551712</v>
       </c>
       <c r="R8" t="n">
-        <v>7246282</v>
+        <v>7246357</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647319</v>
+        <v>122647320</v>
       </c>
       <c r="B9" t="n">
-        <v>97309</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,7 +1465,7 @@
         <v>551763</v>
       </c>
       <c r="R9" t="n">
-        <v>7246423</v>
+        <v>7246410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647260</v>
+        <v>122647316</v>
       </c>
       <c r="B10" t="n">
-        <v>91882</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551667</v>
+        <v>551762</v>
       </c>
       <c r="R10" t="n">
-        <v>7246311</v>
+        <v>7246403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647279</v>
+        <v>122647258</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551715</v>
+        <v>551667</v>
       </c>
       <c r="R11" t="n">
-        <v>7246376</v>
+        <v>7246282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647278</v>
+        <v>122647259</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551729</v>
+        <v>551667</v>
       </c>
       <c r="R12" t="n">
-        <v>7246354</v>
+        <v>7246288</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647314</v>
+        <v>122647257</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551740</v>
+        <v>551664</v>
       </c>
       <c r="R13" t="n">
-        <v>7246367</v>
+        <v>7246288</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,6 +1932,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647320</v>
+        <v>122647122</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551763</v>
+        <v>551874</v>
       </c>
       <c r="R14" t="n">
-        <v>7246410</v>
+        <v>7246567</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647122</v>
+        <v>122647123</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551874</v>
+        <v>551884</v>
       </c>
       <c r="R15" t="n">
-        <v>7246567</v>
+        <v>7246571</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647315</v>
+        <v>122647279</v>
       </c>
       <c r="B16" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551738</v>
+        <v>551715</v>
       </c>
       <c r="R16" t="n">
-        <v>7246373</v>
+        <v>7246376</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647277</v>
+        <v>122647261</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551716</v>
+        <v>551687</v>
       </c>
       <c r="R17" t="n">
-        <v>7246359</v>
+        <v>7246322</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647294</v>
+        <v>122647318</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551726</v>
+        <v>551748</v>
       </c>
       <c r="R18" t="n">
-        <v>7246369</v>
+        <v>7246419</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,11 +2467,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647292</v>
+        <v>122647278</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>74863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,21 +2513,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551712</v>
+        <v>551729</v>
       </c>
       <c r="R19" t="n">
-        <v>7246357</v>
+        <v>7246354</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647316</v>
+        <v>122647260</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>91882</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551762</v>
+        <v>551667</v>
       </c>
       <c r="R20" t="n">
-        <v>7246403</v>
+        <v>7246311</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647276</v>
+        <v>122647294</v>
       </c>
       <c r="B21" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2725,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551728</v>
+        <v>551726</v>
       </c>
       <c r="R21" t="n">
-        <v>7246341</v>
+        <v>7246369</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,6 +2785,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647123</v>
+        <v>122647277</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551884</v>
+        <v>551716</v>
       </c>
       <c r="R22" t="n">
-        <v>7246571</v>
+        <v>7246359</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647318</v>
+        <v>122647262</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>90940</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551748</v>
+        <v>551686</v>
       </c>
       <c r="R23" t="n">
-        <v>7246419</v>
+        <v>7246330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647316</v>
+        <v>122647258</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551762</v>
+        <v>551667</v>
       </c>
       <c r="R10" t="n">
-        <v>7246403</v>
+        <v>7246282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,6 +1604,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647258</v>
+        <v>122647316</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551667</v>
+        <v>551762</v>
       </c>
       <c r="R11" t="n">
-        <v>7246282</v>
+        <v>7246403</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647258</v>
+        <v>122647316</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551667</v>
+        <v>551762</v>
       </c>
       <c r="R10" t="n">
-        <v>7246282</v>
+        <v>7246403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,11 +1604,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647316</v>
+        <v>122647258</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551762</v>
+        <v>551667</v>
       </c>
       <c r="R11" t="n">
-        <v>7246403</v>
+        <v>7246282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647315</v>
+        <v>122647293</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551738</v>
+        <v>551730</v>
       </c>
       <c r="R2" t="n">
-        <v>7246373</v>
+        <v>7246351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647276</v>
+        <v>122647320</v>
       </c>
       <c r="B3" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551728</v>
+        <v>551763</v>
       </c>
       <c r="R3" t="n">
-        <v>7246341</v>
+        <v>7246410</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647295</v>
+        <v>122647276</v>
       </c>
       <c r="B4" t="n">
-        <v>57589</v>
+        <v>90940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551732</v>
+        <v>551728</v>
       </c>
       <c r="R4" t="n">
-        <v>7246362</v>
+        <v>7246341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647319</v>
+        <v>122647258</v>
       </c>
       <c r="B5" t="n">
-        <v>97311</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551763</v>
+        <v>551667</v>
       </c>
       <c r="R5" t="n">
-        <v>7246423</v>
+        <v>7246282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647314</v>
+        <v>122647278</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551740</v>
+        <v>551729</v>
       </c>
       <c r="R6" t="n">
-        <v>7246367</v>
+        <v>7246354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647293</v>
+        <v>122647316</v>
       </c>
       <c r="B7" t="n">
         <v>90962</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551730</v>
+        <v>551762</v>
       </c>
       <c r="R7" t="n">
-        <v>7246351</v>
+        <v>7246403</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647292</v>
+        <v>122647257</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551712</v>
+        <v>551664</v>
       </c>
       <c r="R8" t="n">
-        <v>7246357</v>
+        <v>7246288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,6 +1392,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647320</v>
+        <v>122647259</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551763</v>
+        <v>551667</v>
       </c>
       <c r="R9" t="n">
-        <v>7246410</v>
+        <v>7246288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1503,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647316</v>
+        <v>122647261</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551762</v>
+        <v>551687</v>
       </c>
       <c r="R10" t="n">
-        <v>7246403</v>
+        <v>7246322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647258</v>
+        <v>122647122</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551667</v>
+        <v>551874</v>
       </c>
       <c r="R11" t="n">
-        <v>7246282</v>
+        <v>7246567</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,11 +1722,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1734,7 +1739,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647259</v>
+        <v>122647123</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551667</v>
+        <v>551884</v>
       </c>
       <c r="R12" t="n">
-        <v>7246288</v>
+        <v>7246571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,11 +1828,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gnag</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647257</v>
+        <v>122647277</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551664</v>
+        <v>551716</v>
       </c>
       <c r="R13" t="n">
-        <v>7246288</v>
+        <v>7246359</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,11 +1932,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647122</v>
+        <v>122647315</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551874</v>
+        <v>551738</v>
       </c>
       <c r="R14" t="n">
-        <v>7246567</v>
+        <v>7246373</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,7 +2057,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2073,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647123</v>
+        <v>122647294</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551884</v>
+        <v>551726</v>
       </c>
       <c r="R15" t="n">
-        <v>7246571</v>
+        <v>7246369</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,6 +2146,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2179,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647279</v>
+        <v>122647314</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551715</v>
+        <v>551740</v>
       </c>
       <c r="R16" t="n">
-        <v>7246376</v>
+        <v>7246367</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647261</v>
+        <v>122647292</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551687</v>
+        <v>551712</v>
       </c>
       <c r="R17" t="n">
-        <v>7246322</v>
+        <v>7246357</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647318</v>
+        <v>122647279</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551748</v>
+        <v>551715</v>
       </c>
       <c r="R18" t="n">
-        <v>7246419</v>
+        <v>7246376</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647278</v>
+        <v>122647262</v>
       </c>
       <c r="B19" t="n">
-        <v>74863</v>
+        <v>90940</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551729</v>
+        <v>551686</v>
       </c>
       <c r="R19" t="n">
-        <v>7246354</v>
+        <v>7246330</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647294</v>
+        <v>122647295</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,20 +2721,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551726</v>
+        <v>551732</v>
       </c>
       <c r="R21" t="n">
-        <v>7246369</v>
+        <v>7246362</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647277</v>
+        <v>122647318</v>
       </c>
       <c r="B22" t="n">
-        <v>74863</v>
+        <v>57631</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551716</v>
+        <v>551748</v>
       </c>
       <c r="R22" t="n">
-        <v>7246359</v>
+        <v>7246419</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647262</v>
+        <v>122647319</v>
       </c>
       <c r="B23" t="n">
-        <v>90940</v>
+        <v>97311</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,25 +2938,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551686</v>
+        <v>551763</v>
       </c>
       <c r="R23" t="n">
-        <v>7246330</v>
+        <v>7246423</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647320</v>
+        <v>122647276</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>90940</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551763</v>
+        <v>551728</v>
       </c>
       <c r="R3" t="n">
-        <v>7246410</v>
+        <v>7246341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647276</v>
+        <v>122647320</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551728</v>
+        <v>551763</v>
       </c>
       <c r="R4" t="n">
-        <v>7246341</v>
+        <v>7246410</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647276</v>
+        <v>122647320</v>
       </c>
       <c r="B3" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551728</v>
+        <v>551763</v>
       </c>
       <c r="R3" t="n">
-        <v>7246341</v>
+        <v>7246410</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647320</v>
+        <v>122647276</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>90940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551763</v>
+        <v>551728</v>
       </c>
       <c r="R4" t="n">
-        <v>7246410</v>
+        <v>7246341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647293</v>
+        <v>122647292</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551730</v>
+        <v>551712</v>
       </c>
       <c r="R2" t="n">
-        <v>7246351</v>
+        <v>7246357</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647320</v>
+        <v>122647279</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551763</v>
+        <v>551715</v>
       </c>
       <c r="R3" t="n">
-        <v>7246410</v>
+        <v>7246376</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647276</v>
+        <v>122647123</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551728</v>
+        <v>551884</v>
       </c>
       <c r="R4" t="n">
-        <v>7246341</v>
+        <v>7246571</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647258</v>
+        <v>122647278</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551667</v>
+        <v>551729</v>
       </c>
       <c r="R5" t="n">
-        <v>7246282</v>
+        <v>7246354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1069,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647278</v>
+        <v>122647320</v>
       </c>
       <c r="B6" t="n">
         <v>74863</v>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551729</v>
+        <v>551763</v>
       </c>
       <c r="R6" t="n">
-        <v>7246354</v>
+        <v>7246410</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647316</v>
+        <v>122647294</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551762</v>
+        <v>551726</v>
       </c>
       <c r="R7" t="n">
-        <v>7246403</v>
+        <v>7246369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647257</v>
+        <v>122647260</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
+        <v>91890</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551664</v>
+        <v>551667</v>
       </c>
       <c r="R8" t="n">
-        <v>7246288</v>
+        <v>7246311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647259</v>
+        <v>122647122</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551667</v>
+        <v>551874</v>
       </c>
       <c r="R9" t="n">
-        <v>7246288</v>
+        <v>7246567</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,11 +1500,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gnag</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1527,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1538,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647261</v>
+        <v>122647277</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551687</v>
+        <v>551716</v>
       </c>
       <c r="R10" t="n">
-        <v>7246322</v>
+        <v>7246359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647122</v>
+        <v>122647257</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>8430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551874</v>
+        <v>551664</v>
       </c>
       <c r="R11" t="n">
-        <v>7246567</v>
+        <v>7246288</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,6 +1712,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gnag</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1739,7 +1734,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647123</v>
+        <v>122647259</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551884</v>
+        <v>551667</v>
       </c>
       <c r="R12" t="n">
-        <v>7246571</v>
+        <v>7246288</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,6 +1823,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnag</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647277</v>
+        <v>122647261</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551716</v>
+        <v>551687</v>
       </c>
       <c r="R13" t="n">
-        <v>7246359</v>
+        <v>7246322</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647315</v>
+        <v>122647314</v>
       </c>
       <c r="B14" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551738</v>
+        <v>551740</v>
       </c>
       <c r="R14" t="n">
-        <v>7246373</v>
+        <v>7246367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647294</v>
+        <v>122647258</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551726</v>
+        <v>551667</v>
       </c>
       <c r="R15" t="n">
-        <v>7246369</v>
+        <v>7246282</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647314</v>
+        <v>122647262</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551740</v>
+        <v>551686</v>
       </c>
       <c r="R16" t="n">
-        <v>7246367</v>
+        <v>7246330</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647292</v>
+        <v>122647316</v>
       </c>
       <c r="B17" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551712</v>
+        <v>551762</v>
       </c>
       <c r="R17" t="n">
-        <v>7246357</v>
+        <v>7246403</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647279</v>
+        <v>122647318</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551715</v>
+        <v>551748</v>
       </c>
       <c r="R18" t="n">
-        <v>7246376</v>
+        <v>7246419</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647262</v>
+        <v>122647319</v>
       </c>
       <c r="B19" t="n">
-        <v>90940</v>
+        <v>97319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551686</v>
+        <v>551763</v>
       </c>
       <c r="R19" t="n">
-        <v>7246330</v>
+        <v>7246423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647260</v>
+        <v>122647293</v>
       </c>
       <c r="B20" t="n">
-        <v>91882</v>
+        <v>90970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551667</v>
+        <v>551730</v>
       </c>
       <c r="R20" t="n">
-        <v>7246311</v>
+        <v>7246351</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647295</v>
+        <v>122647276</v>
       </c>
       <c r="B21" t="n">
-        <v>57589</v>
+        <v>90948</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,25 +2721,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551732</v>
+        <v>551728</v>
       </c>
       <c r="R21" t="n">
-        <v>7246362</v>
+        <v>7246341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,11 +2785,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647318</v>
+        <v>122647315</v>
       </c>
       <c r="B22" t="n">
-        <v>57631</v>
+        <v>90948</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551748</v>
+        <v>551738</v>
       </c>
       <c r="R22" t="n">
-        <v>7246419</v>
+        <v>7246373</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647319</v>
+        <v>122647295</v>
       </c>
       <c r="B23" t="n">
-        <v>97311</v>
+        <v>57589</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2937,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551763</v>
+        <v>551732</v>
       </c>
       <c r="R23" t="n">
-        <v>7246423</v>
+        <v>7246362</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,6 +2997,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647123</v>
+        <v>122647278</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551884</v>
+        <v>551729</v>
       </c>
       <c r="R4" t="n">
-        <v>7246571</v>
+        <v>7246354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647278</v>
+        <v>122647320</v>
       </c>
       <c r="B5" t="n">
         <v>74863</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551729</v>
+        <v>551763</v>
       </c>
       <c r="R5" t="n">
-        <v>7246354</v>
+        <v>7246410</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647320</v>
+        <v>122647123</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551763</v>
+        <v>551884</v>
       </c>
       <c r="R6" t="n">
-        <v>7246410</v>
+        <v>7246571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647292</v>
+        <v>122647278</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551712</v>
+        <v>551729</v>
       </c>
       <c r="R2" t="n">
-        <v>7246357</v>
+        <v>7246354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647279</v>
+        <v>122647315</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551715</v>
+        <v>551738</v>
       </c>
       <c r="R3" t="n">
-        <v>7246376</v>
+        <v>7246373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647278</v>
+        <v>122647259</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551729</v>
+        <v>551667</v>
       </c>
       <c r="R4" t="n">
-        <v>7246354</v>
+        <v>7246288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647320</v>
+        <v>122647294</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551763</v>
+        <v>551726</v>
       </c>
       <c r="R5" t="n">
-        <v>7246410</v>
+        <v>7246369</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647123</v>
+        <v>122647314</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551884</v>
+        <v>551740</v>
       </c>
       <c r="R6" t="n">
-        <v>7246571</v>
+        <v>7246367</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1204,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647294</v>
+        <v>122647316</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551726</v>
+        <v>551762</v>
       </c>
       <c r="R7" t="n">
-        <v>7246369</v>
+        <v>7246403</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647260</v>
+        <v>122647262</v>
       </c>
       <c r="B8" t="n">
-        <v>91890</v>
+        <v>90948</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551667</v>
+        <v>551686</v>
       </c>
       <c r="R8" t="n">
-        <v>7246311</v>
+        <v>7246330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647122</v>
+        <v>122647293</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551874</v>
+        <v>551730</v>
       </c>
       <c r="R9" t="n">
-        <v>7246567</v>
+        <v>7246351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1522,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647277</v>
+        <v>122647295</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>57589</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551716</v>
+        <v>551732</v>
       </c>
       <c r="R10" t="n">
-        <v>7246359</v>
+        <v>7246362</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,6 +1609,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647257</v>
+        <v>122647258</v>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551664</v>
+        <v>551667</v>
       </c>
       <c r="R11" t="n">
-        <v>7246288</v>
+        <v>7246282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,7 +1724,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647259</v>
+        <v>122647123</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551667</v>
+        <v>551884</v>
       </c>
       <c r="R12" t="n">
-        <v>7246288</v>
+        <v>7246571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,11 +1833,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gnag</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1845,7 +1850,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1856,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647261</v>
+        <v>122647257</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1873,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551687</v>
+        <v>551664</v>
       </c>
       <c r="R13" t="n">
-        <v>7246322</v>
+        <v>7246288</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,6 +1937,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1972,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647314</v>
+        <v>122647261</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2002,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551740</v>
+        <v>551687</v>
       </c>
       <c r="R14" t="n">
-        <v>7246367</v>
+        <v>7246322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647258</v>
+        <v>122647277</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,21 +2094,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551667</v>
+        <v>551716</v>
       </c>
       <c r="R15" t="n">
-        <v>7246282</v>
+        <v>7246359</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,11 +2154,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647262</v>
+        <v>122647260</v>
       </c>
       <c r="B16" t="n">
-        <v>90948</v>
+        <v>91890</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,25 +2196,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551686</v>
+        <v>551667</v>
       </c>
       <c r="R16" t="n">
-        <v>7246330</v>
+        <v>7246311</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647316</v>
+        <v>122647320</v>
       </c>
       <c r="B17" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551762</v>
+        <v>551763</v>
       </c>
       <c r="R17" t="n">
-        <v>7246403</v>
+        <v>7246410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647318</v>
+        <v>122647292</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551748</v>
+        <v>551712</v>
       </c>
       <c r="R18" t="n">
-        <v>7246419</v>
+        <v>7246357</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647319</v>
+        <v>122647122</v>
       </c>
       <c r="B19" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551763</v>
+        <v>551874</v>
       </c>
       <c r="R19" t="n">
-        <v>7246423</v>
+        <v>7246567</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2597,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2603,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647293</v>
+        <v>122647279</v>
       </c>
       <c r="B20" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,21 +2624,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551730</v>
+        <v>551715</v>
       </c>
       <c r="R20" t="n">
-        <v>7246351</v>
+        <v>7246376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647315</v>
+        <v>122647318</v>
       </c>
       <c r="B22" t="n">
-        <v>90948</v>
+        <v>57631</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551738</v>
+        <v>551748</v>
       </c>
       <c r="R22" t="n">
-        <v>7246373</v>
+        <v>7246419</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647295</v>
+        <v>122647319</v>
       </c>
       <c r="B23" t="n">
-        <v>57589</v>
+        <v>97319</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551732</v>
+        <v>551763</v>
       </c>
       <c r="R23" t="n">
-        <v>7246362</v>
+        <v>7246423</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,11 +3002,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647278</v>
+        <v>122647315</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>90948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551729</v>
+        <v>551738</v>
       </c>
       <c r="R2" t="n">
-        <v>7246354</v>
+        <v>7246373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647315</v>
+        <v>122647259</v>
       </c>
       <c r="B3" t="n">
-        <v>90948</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551738</v>
+        <v>551667</v>
       </c>
       <c r="R3" t="n">
-        <v>7246373</v>
+        <v>7246288</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647259</v>
+        <v>122647278</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551667</v>
+        <v>551729</v>
       </c>
       <c r="R4" t="n">
-        <v>7246288</v>
+        <v>7246354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647294</v>
+        <v>122647314</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551726</v>
+        <v>551740</v>
       </c>
       <c r="R5" t="n">
-        <v>7246369</v>
+        <v>7246367</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647314</v>
+        <v>122647294</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551740</v>
+        <v>551726</v>
       </c>
       <c r="R6" t="n">
-        <v>7246367</v>
+        <v>7246369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647276</v>
+        <v>122647318</v>
       </c>
       <c r="B21" t="n">
-        <v>90948</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551728</v>
+        <v>551748</v>
       </c>
       <c r="R21" t="n">
-        <v>7246341</v>
+        <v>7246419</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647318</v>
+        <v>122647276</v>
       </c>
       <c r="B22" t="n">
-        <v>57631</v>
+        <v>90948</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551748</v>
+        <v>551728</v>
       </c>
       <c r="R22" t="n">
-        <v>7246419</v>
+        <v>7246341</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647315</v>
+        <v>122647320</v>
       </c>
       <c r="B2" t="n">
-        <v>90948</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551738</v>
+        <v>551763</v>
       </c>
       <c r="R2" t="n">
-        <v>7246373</v>
+        <v>7246410</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647259</v>
+        <v>122647279</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551667</v>
+        <v>551715</v>
       </c>
       <c r="R3" t="n">
-        <v>7246288</v>
+        <v>7246376</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647278</v>
+        <v>122647262</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>90948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551729</v>
+        <v>551686</v>
       </c>
       <c r="R4" t="n">
-        <v>7246354</v>
+        <v>7246330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647314</v>
+        <v>122647293</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551740</v>
+        <v>551730</v>
       </c>
       <c r="R5" t="n">
-        <v>7246367</v>
+        <v>7246351</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647294</v>
+        <v>122647260</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>91890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551726</v>
+        <v>551667</v>
       </c>
       <c r="R6" t="n">
-        <v>7246369</v>
+        <v>7246311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647316</v>
+        <v>122647318</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551762</v>
+        <v>551748</v>
       </c>
       <c r="R7" t="n">
-        <v>7246403</v>
+        <v>7246419</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647262</v>
+        <v>122647258</v>
       </c>
       <c r="B8" t="n">
-        <v>90948</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551686</v>
+        <v>551667</v>
       </c>
       <c r="R8" t="n">
-        <v>7246330</v>
+        <v>7246282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647293</v>
+        <v>122647294</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551730</v>
+        <v>551726</v>
       </c>
       <c r="R9" t="n">
-        <v>7246351</v>
+        <v>7246369</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,6 +1498,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647295</v>
+        <v>122647292</v>
       </c>
       <c r="B10" t="n">
-        <v>57589</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551732</v>
+        <v>551712</v>
       </c>
       <c r="R10" t="n">
-        <v>7246362</v>
+        <v>7246357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,11 +1609,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647258</v>
+        <v>122647261</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551667</v>
+        <v>551687</v>
       </c>
       <c r="R11" t="n">
-        <v>7246282</v>
+        <v>7246322</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647257</v>
+        <v>122647278</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551664</v>
+        <v>551729</v>
       </c>
       <c r="R13" t="n">
-        <v>7246288</v>
+        <v>7246354</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,11 +1927,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647261</v>
+        <v>122647295</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551687</v>
+        <v>551732</v>
       </c>
       <c r="R14" t="n">
-        <v>7246322</v>
+        <v>7246362</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,6 +2033,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647277</v>
+        <v>122647315</v>
       </c>
       <c r="B15" t="n">
-        <v>74863</v>
+        <v>90948</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,21 +2084,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2118,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551716</v>
+        <v>551738</v>
       </c>
       <c r="R15" t="n">
-        <v>7246359</v>
+        <v>7246373</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647260</v>
+        <v>122647314</v>
       </c>
       <c r="B16" t="n">
-        <v>91890</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,25 +2186,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2224,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551667</v>
+        <v>551740</v>
       </c>
       <c r="R16" t="n">
-        <v>7246311</v>
+        <v>7246367</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647320</v>
+        <v>122647259</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>5173</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,25 +2292,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551763</v>
+        <v>551667</v>
       </c>
       <c r="R17" t="n">
-        <v>7246410</v>
+        <v>7246288</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,6 +2356,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647292</v>
+        <v>122647257</v>
       </c>
       <c r="B18" t="n">
-        <v>90970</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,25 +2403,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551712</v>
+        <v>551664</v>
       </c>
       <c r="R18" t="n">
-        <v>7246357</v>
+        <v>7246288</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,6 +2467,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647122</v>
+        <v>122647319</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551874</v>
+        <v>551763</v>
       </c>
       <c r="R19" t="n">
-        <v>7246567</v>
+        <v>7246423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647279</v>
+        <v>122647316</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2624,21 +2624,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551715</v>
+        <v>551762</v>
       </c>
       <c r="R20" t="n">
-        <v>7246376</v>
+        <v>7246403</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647318</v>
+        <v>122647277</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551748</v>
+        <v>551716</v>
       </c>
       <c r="R21" t="n">
-        <v>7246419</v>
+        <v>7246359</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647276</v>
+        <v>122647122</v>
       </c>
       <c r="B22" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551728</v>
+        <v>551874</v>
       </c>
       <c r="R22" t="n">
-        <v>7246341</v>
+        <v>7246567</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647319</v>
+        <v>122647276</v>
       </c>
       <c r="B23" t="n">
-        <v>97319</v>
+        <v>90948</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,25 +2938,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551763</v>
+        <v>551728</v>
       </c>
       <c r="R23" t="n">
-        <v>7246423</v>
+        <v>7246341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 15343-2023 artfynd.xlsx
+++ b/artfynd/A 15343-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647320</v>
+        <v>122647262</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551763</v>
+        <v>551686</v>
       </c>
       <c r="R2" t="n">
-        <v>7246410</v>
+        <v>7246330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647279</v>
+        <v>122647276</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551715</v>
+        <v>551728</v>
       </c>
       <c r="R3" t="n">
-        <v>7246376</v>
+        <v>7246341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647262</v>
+        <v>122647315</v>
       </c>
       <c r="B4" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551686</v>
+        <v>551738</v>
       </c>
       <c r="R4" t="n">
-        <v>7246330</v>
+        <v>7246373</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647293</v>
+        <v>122647260</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551730</v>
+        <v>551667</v>
       </c>
       <c r="R5" t="n">
-        <v>7246351</v>
+        <v>7246311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647260</v>
+        <v>122647122</v>
       </c>
       <c r="B6" t="n">
-        <v>91890</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551667</v>
+        <v>551874</v>
       </c>
       <c r="R6" t="n">
-        <v>7246311</v>
+        <v>7246567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1169,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647318</v>
+        <v>122647261</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551748</v>
+        <v>551687</v>
       </c>
       <c r="R7" t="n">
-        <v>7246419</v>
+        <v>7246322</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647258</v>
+        <v>122647279</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551667</v>
+        <v>551715</v>
       </c>
       <c r="R8" t="n">
-        <v>7246282</v>
+        <v>7246376</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1352,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647294</v>
+        <v>122647314</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551726</v>
+        <v>551740</v>
       </c>
       <c r="R9" t="n">
-        <v>7246369</v>
+        <v>7246367</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,11 +1453,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647292</v>
+        <v>122647277</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551712</v>
+        <v>551716</v>
       </c>
       <c r="R10" t="n">
-        <v>7246357</v>
+        <v>7246359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647261</v>
+        <v>122647278</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551687</v>
+        <v>551729</v>
       </c>
       <c r="R11" t="n">
-        <v>7246322</v>
+        <v>7246354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647123</v>
+        <v>122647320</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551884</v>
+        <v>551763</v>
       </c>
       <c r="R12" t="n">
-        <v>7246571</v>
+        <v>7246410</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1840,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1851,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647278</v>
+        <v>122647123</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551729</v>
+        <v>551884</v>
       </c>
       <c r="R13" t="n">
-        <v>7246354</v>
+        <v>7246571</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1876,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1957,32 +1887,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647295</v>
+        <v>122647258</v>
       </c>
       <c r="B14" t="n">
-        <v>57589</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1997,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551732</v>
+        <v>551667</v>
       </c>
       <c r="R14" t="n">
-        <v>7246362</v>
+        <v>7246282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +1962,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>3 st födosökande</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,15 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647315</v>
+        <v>122647294</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,21 +2004,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551738</v>
+        <v>551726</v>
       </c>
       <c r="R15" t="n">
-        <v>7246373</v>
+        <v>7246369</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,6 +2064,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,37 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647314</v>
+        <v>122647259</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551740</v>
+        <v>551667</v>
       </c>
       <c r="R16" t="n">
-        <v>7246367</v>
+        <v>7246288</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,6 +2170,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,37 +2205,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647259</v>
+        <v>122647318</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551667</v>
+        <v>551748</v>
       </c>
       <c r="R17" t="n">
-        <v>7246288</v>
+        <v>7246419</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,11 +2276,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,37 +2306,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647257</v>
+        <v>122647295</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551664</v>
+        <v>551732</v>
       </c>
       <c r="R18" t="n">
-        <v>7246288</v>
+        <v>7246362</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2381,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>3 st födosökande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,15 +2412,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647319</v>
+        <v>122647257</v>
       </c>
       <c r="B19" t="n">
-        <v>97319</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,21 +2423,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2447,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551763</v>
+        <v>551664</v>
       </c>
       <c r="R19" t="n">
-        <v>7246423</v>
+        <v>7246288</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,6 +2483,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,37 +2518,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647316</v>
+        <v>122647319</v>
       </c>
       <c r="B20" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551762</v>
+        <v>551763</v>
       </c>
       <c r="R20" t="n">
-        <v>7246403</v>
+        <v>7246423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,324 +2612,6 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>122647277</v>
-      </c>
-      <c r="B21" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>551716</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7246359</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Sam Keith</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>122647122</v>
-      </c>
-      <c r="B22" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>551874</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7246567</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Hannah Norman</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>122647276</v>
-      </c>
-      <c r="B23" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>551728</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7246341</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Sam Keith</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
         <is>
           <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
         </is>
